--- a/output/pdf_financials_xlsx/ABZ.xlsx
+++ b/output/pdf_financials_xlsx/ABZ.xlsx
@@ -5785,46 +5785,46 @@
         <v>0.178076</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.273545</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.29858</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.29858</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.29858</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.29858</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.441684</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.664891</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.761555</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.980258</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.410321</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.410321</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.725847</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.818455</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.820224</v>
       </c>
     </row>
     <row r="93">
@@ -9042,7 +9042,11 @@
           <t>Share-based payment reserves</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -10040,7 +10044,11 @@
           <t>Share-based payment reserves</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10414,7 +10422,11 @@
           <t>Share-based payment reserves</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -10860,7 +10872,11 @@
           <t>Share-based payment reserves</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ABZ.xlsx
+++ b/output/pdf_financials_xlsx/ABZ.xlsx
@@ -2371,52 +2371,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.499821</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.355201</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.203709</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.370386</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.146719</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.123277</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.056888</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.004891</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.422768</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.233589</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.075126</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.065548</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.040165</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.001487</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.001777</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.000544</v>
       </c>
     </row>
     <row r="35">
@@ -2481,52 +2481,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.499821</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.355201</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.203709</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.370386</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.146719</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.123277</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.056888</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.004891</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.422768</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.233589</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.075126</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.065548</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.040165</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.001487</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.001777</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.000544</v>
       </c>
     </row>
     <row r="37">
@@ -3141,52 +3141,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.499821</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.355201</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.387129</v>
+        <v>0.016743</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.163569</v>
+        <v>0.01685</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.136777</v>
+        <v>0.0135</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.057388</v>
+        <v>0.0005</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.006302</v>
+        <v>0.001411</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.422921</v>
+        <v>0.000153</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.264865</v>
+        <v>0.031276</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.093046</v>
+        <v>0.01792</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.070327</v>
+        <v>0.004779</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.040165</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.001487</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.001777</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.000544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -8672,7 +8672,11 @@
           <t>Reclamation deposit (Note 7)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -9316,7 +9320,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -9576,7 +9580,11 @@
           <t>Reclamation deposit (Note 6)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -14548,7 +14556,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ABZ.xlsx
+++ b/output/pdf_financials_xlsx/ABZ.xlsx
@@ -18404,7 +18404,11 @@
           <t>Proceeds from share issuance -</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
